--- a/data/trans_orig/P1402-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2007</t>
+          <t>Población con diagnóstico de diabetes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55668</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>65779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99963</t>
+          <t>101269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640847</t>
+          <t>642020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664118</t>
+          <t>664601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632683</t>
+          <t>633620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658442</t>
+          <t>657796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1282400</t>
+          <t>1281094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1317667</t>
+          <t>1316584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82820</t>
+          <t>82306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61372</t>
+          <t>60604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95042</t>
+          <t>95929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122314</t>
+          <t>120090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166698</t>
+          <t>163252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>878980</t>
+          <t>879494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>911698</t>
+          <t>910689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>873351</t>
+          <t>872464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>907021</t>
+          <t>907789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1763495</t>
+          <t>1766941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1807879</t>
+          <t>1810103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59150</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59527</t>
+          <t>57933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94356</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636061</t>
+          <t>636338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657527</t>
+          <t>657886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624691</t>
+          <t>624415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650104</t>
+          <t>650091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1267994</t>
+          <t>1269632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302823</t>
+          <t>1304417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
+          <t>39599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64786</t>
+          <t>65066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51316</t>
+          <t>51493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83550</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>116614</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>97838</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>137300</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>116614</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>97320</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>137901</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>877436</t>
+          <t>877156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902981</t>
+          <t>902623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>955062</t>
+          <t>956459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>987296</t>
+          <t>987119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1864220</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1843534</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1882996</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>95,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1864220</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1842933</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1883514</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209270</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>201167</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259997</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376434</t>
+          <t>380100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453261</t>
+          <t>455760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3067273</t>
+          <t>3065741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3117822</t>
+          <t>3115502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3119200</t>
+          <t>3120441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3177930</t>
+          <t>3178030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6202480</t>
+          <t>6199981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6279307</t>
+          <t>6275641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2012</t>
+          <t>Población con diagnóstico de diabetes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>63873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37142</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>65653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80090</t>
+          <t>79627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122127</t>
+          <t>118661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>639189</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667731</t>
+          <t>667298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632377</t>
+          <t>631397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>659908</t>
+          <t>660628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1278392</t>
+          <t>1281858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1320429</t>
+          <t>1320892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83998</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65797</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102257</t>
+          <t>102375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127995</t>
+          <t>125846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179193</t>
+          <t>172661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933949</t>
+          <t>934135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966456</t>
+          <t>965661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926716</t>
+          <t>926598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>963176</t>
+          <t>963342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1867728</t>
+          <t>1874260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1918926</t>
+          <t>1921075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70772</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>51849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82587</t>
+          <t>83108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99288</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>146261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>686851</t>
+          <t>683615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>716780</t>
+          <t>715650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>694587</t>
+          <t>694066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>726465</t>
+          <t>725325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1391743</t>
+          <t>1388536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1435509</t>
+          <t>1434412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72278</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108226</t>
+          <t>107377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87542</t>
+          <t>89406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129513</t>
+          <t>129409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169593</t>
+          <t>168435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226798</t>
+          <t>223465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839513</t>
+          <t>840362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875461</t>
+          <t>878088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>922388</t>
+          <t>922492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964359</t>
+          <t>962495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1772842</t>
+          <t>1776175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1830047</t>
+          <t>1831205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>226149</t>
+          <t>226653</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290753</t>
+          <t>288927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274632</t>
+          <t>274080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340769</t>
+          <t>342156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>517140</t>
+          <t>518037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>613135</t>
+          <t>611320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3136026</t>
+          <t>3137852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3200630</t>
+          <t>3200126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3214329</t>
+          <t>3212942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3280466</t>
+          <t>3281018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6368742</t>
+          <t>6370557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6464737</t>
+          <t>6463840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2016</t>
+          <t>Población con diagnóstico de diabetes en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>50161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82425</t>
+          <t>79958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>73325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101271</t>
+          <t>101529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143908</t>
+          <t>142783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592375</t>
+          <t>594842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623319</t>
+          <t>624639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602631</t>
+          <t>599514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632003</t>
+          <t>630536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203731</t>
+          <t>1204856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246368</t>
+          <t>1246110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65754</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105479</t>
+          <t>108306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145753</t>
+          <t>145386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200306</t>
+          <t>198189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>916627</t>
+          <t>917316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953450</t>
+          <t>952822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>937434</t>
+          <t>934607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>977159</t>
+          <t>973506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1865038</t>
+          <t>1867155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1919591</t>
+          <t>1919958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58520</t>
+          <t>57647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92876</t>
+          <t>92710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52616</t>
+          <t>53170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86840</t>
+          <t>87315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123092</t>
+          <t>121317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171311</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666676</t>
+          <t>666842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701032</t>
+          <t>701905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698171</t>
+          <t>697696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>732395</t>
+          <t>731841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373252</t>
+          <t>1373216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1421471</t>
+          <t>1423246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58340</t>
+          <t>58190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89072</t>
+          <t>88395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68406</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106099</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135886</t>
+          <t>136636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188884</t>
+          <t>187789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848495</t>
+          <t>849172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879227</t>
+          <t>879377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937680</t>
+          <t>934766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975373</t>
+          <t>973408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1792462</t>
+          <t>1793557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1845460</t>
+          <t>1844710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>267555</t>
+          <t>268492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>334290</t>
+          <t>332542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266253</t>
+          <t>263158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335160</t>
+          <t>337702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>546898</t>
+          <t>548885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>641709</t>
+          <t>646291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3060060</t>
+          <t>3061808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3126795</t>
+          <t>3125858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3209382</t>
+          <t>3206840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3278289</t>
+          <t>3281384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6297183</t>
+          <t>6292601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6391994</t>
+          <t>6390007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2023</t>
+          <t>Población con diagnóstico de diabetes en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79085</t>
+          <t>78293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>77280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115365</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148055</t>
+          <t>147983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554934</t>
+          <t>555726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>582497</t>
+          <t>581660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>597089</t>
+          <t>598090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618380</t>
+          <t>619373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1161334</t>
+          <t>1161406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1194024</t>
+          <t>1194490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113572</t>
+          <t>112521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65713</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103906</t>
+          <t>99356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>189604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1078484</t>
+          <t>1079535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1146790</t>
+          <t>1149906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866837</t>
+          <t>867661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>891143</t>
+          <t>892378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1959693</t>
+          <t>1959308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2045006</t>
+          <t>2049556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49590</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>79028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64536</t>
+          <t>64614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>69541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132864</t>
+          <t>132160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625308</t>
+          <t>623937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653375</t>
+          <t>652285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>868218</t>
+          <t>868140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909367</t>
+          <t>910677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1502854</t>
+          <t>1503558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1568474</t>
+          <t>1566177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73824</t>
+          <t>73010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104994</t>
+          <t>105630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59787</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89422</t>
+          <t>88146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141699</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187938</t>
+          <t>185347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817966</t>
+          <t>817330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849136</t>
+          <t>849950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002094</t>
+          <t>1003370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031729</t>
+          <t>1031501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1826537</t>
+          <t>1829128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872776</t>
+          <t>1872516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231104</t>
+          <t>235490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339721</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>215392</t>
+          <t>210216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292618</t>
+          <t>294073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>484173</t>
+          <t>484867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>617312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3112279</t>
+          <t>3112379</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220896</t>
+          <t>3216510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3363877</t>
+          <t>3362422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3441103</t>
+          <t>3446279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6493521</t>
+          <t>6491183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6624322</t>
+          <t>6623628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1402-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29411</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>53155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30555</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65779</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101269</t>
+          <t>98243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642020</t>
+          <t>640857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664601</t>
+          <t>665220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633620</t>
+          <t>632363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657796</t>
+          <t>658313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1281094</t>
+          <t>1284120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1316584</t>
+          <t>1317638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82306</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60604</t>
+          <t>60231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95929</t>
+          <t>94673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120090</t>
+          <t>118574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163252</t>
+          <t>166384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>879494</t>
+          <t>877744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>910689</t>
+          <t>911232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>872464</t>
+          <t>873720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>907789</t>
+          <t>908162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1766941</t>
+          <t>1763809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1810103</t>
+          <t>1811619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>43213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>58192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>61100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92718</t>
+          <t>94857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636338</t>
+          <t>635296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657886</t>
+          <t>657963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624415</t>
+          <t>625649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650091</t>
+          <t>650400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1269632</t>
+          <t>1267493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304417</t>
+          <t>1301250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>64756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51493</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82153</t>
+          <t>83893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>116614</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>98226</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>139156</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>116614</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>97838</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>137300</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>877156</t>
+          <t>877466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902623</t>
+          <t>903562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>956459</t>
+          <t>954719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>987119</t>
+          <t>987035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1864220</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1841678</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1882608</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>95,04%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1864220</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1843534</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1882996</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161041</t>
+          <t>163060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210802</t>
+          <t>212361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258756</t>
+          <t>255318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380100</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>455760</t>
+          <t>457589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3065741</t>
+          <t>3064182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3115502</t>
+          <t>3113483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3120441</t>
+          <t>3123879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3178030</t>
+          <t>3177658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6199981</t>
+          <t>6198152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6275641</t>
+          <t>6277979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63873</t>
+          <t>62033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65653</t>
+          <t>65089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>79870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>118785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>639596</t>
+          <t>641436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667298</t>
+          <t>668994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631397</t>
+          <t>631961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660628</t>
+          <t>659153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1281858</t>
+          <t>1281734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1320892</t>
+          <t>1320649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83812</t>
+          <t>83966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>66370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>102178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>127547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172661</t>
+          <t>173345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>934135</t>
+          <t>933981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>965661</t>
+          <t>965582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926598</t>
+          <t>926795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>963342</t>
+          <t>962603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1874260</t>
+          <t>1873576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921075</t>
+          <t>1919374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>41135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74008</t>
+          <t>72460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83108</t>
+          <t>81738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100385</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146261</t>
+          <t>144974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683615</t>
+          <t>685163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>715650</t>
+          <t>716488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>694066</t>
+          <t>695436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>725325</t>
+          <t>726072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388536</t>
+          <t>1389823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1434412</t>
+          <t>1434019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>70606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107377</t>
+          <t>107521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89406</t>
+          <t>90515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129409</t>
+          <t>131148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168435</t>
+          <t>171888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223465</t>
+          <t>226019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>840362</t>
+          <t>840218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878088</t>
+          <t>877133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>922492</t>
+          <t>920753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>962495</t>
+          <t>961386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1776175</t>
+          <t>1773621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1831205</t>
+          <t>1827752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>226653</t>
+          <t>226560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288927</t>
+          <t>292023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274080</t>
+          <t>273925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342156</t>
+          <t>343177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518037</t>
+          <t>521469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>611320</t>
+          <t>609828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3137852</t>
+          <t>3134756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3200126</t>
+          <t>3200219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3212942</t>
+          <t>3211921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3281018</t>
+          <t>3281173</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6370557</t>
+          <t>6372049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6463840</t>
+          <t>6460408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79958</t>
+          <t>80319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73325</t>
+          <t>71102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>99678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142783</t>
+          <t>144051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>594842</t>
+          <t>594481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>624639</t>
+          <t>624661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599514</t>
+          <t>601737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630536</t>
+          <t>630970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1204856</t>
+          <t>1203588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246110</t>
+          <t>1247961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>70265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69407</t>
+          <t>66279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108306</t>
+          <t>104940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145386</t>
+          <t>145862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198189</t>
+          <t>198224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>917316</t>
+          <t>916538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>952822</t>
+          <t>952166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>934607</t>
+          <t>937973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>973506</t>
+          <t>976634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1867155</t>
+          <t>1867120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1919958</t>
+          <t>1919482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92710</t>
+          <t>92733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53170</t>
+          <t>53172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87315</t>
+          <t>88032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121317</t>
+          <t>123477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171347</t>
+          <t>171500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666842</t>
+          <t>666819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701905</t>
+          <t>701116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697696</t>
+          <t>696979</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>731841</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373216</t>
+          <t>1373063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1423246</t>
+          <t>1421086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88395</t>
+          <t>89404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>70544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109013</t>
+          <t>107979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136636</t>
+          <t>133964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187789</t>
+          <t>184421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849172</t>
+          <t>848163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879377</t>
+          <t>879038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>934766</t>
+          <t>935800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>973408</t>
+          <t>973235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1793557</t>
+          <t>1796925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1844710</t>
+          <t>1847382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268492</t>
+          <t>266855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332542</t>
+          <t>331080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +6014,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>297179</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>262473</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>336372</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>594895</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>548676</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>639499</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>297179</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>263158</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>337702</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>594895</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>548885</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>646291</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3061808</t>
+          <t>3063270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3125858</t>
+          <t>3127495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3206840</t>
+          <t>3208170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3281384</t>
+          <t>3282069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6292601</t>
+          <t>6299393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6390007</t>
+          <t>6390216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>64185</t>
+          <t>69535</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52359</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>84696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,22 +6604,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>60721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77280</t>
+          <t>83846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>130502</t>
+          <t>140654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114899</t>
+          <t>123996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147983</t>
+          <t>159415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>569834</t>
+          <t>619559</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555726</t>
+          <t>604398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>581660</t>
+          <t>632037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,22 +6717,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>609053</t>
+          <t>661603</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598090</t>
+          <t>648876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>619373</t>
+          <t>672001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1178887</t>
+          <t>1281162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1161406</t>
+          <t>1262401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1194490</t>
+          <t>1297820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634019</t>
+          <t>689094</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634019</t>
+          <t>689094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634019</t>
+          <t>689094</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309389</t>
+          <t>1421816</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309389</t>
+          <t>1421816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309389</t>
+          <t>1421816</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>77261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112521</t>
+          <t>111747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,22 +6947,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76629</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>72068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89195</t>
+          <t>99567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>159930</t>
+          <t>178060</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>159466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189604</t>
+          <t>203597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1108755</t>
+          <t>955145</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1079535</t>
+          <t>936166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1149906</t>
+          <t>970652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,27 +7060,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>880227</t>
+          <t>984212</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>867661</t>
+          <t>969936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>892378</t>
+          <t>997435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1988982</t>
+          <t>1939356</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1959308</t>
+          <t>1913819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049556</t>
+          <t>1957950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956856</t>
+          <t>1069503</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956856</t>
+          <t>1069503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956856</t>
+          <t>1069503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148912</t>
+          <t>2117416</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148912</t>
+          <t>2117416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148912</t>
+          <t>2117416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>71007</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50680</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79028</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64614</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109590</t>
+          <t>122973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69541</t>
+          <t>105679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132160</t>
+          <t>143400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>639682</t>
+          <t>730210</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623937</t>
+          <t>712162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652285</t>
+          <t>743926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>886447</t>
+          <t>759605</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>868140</t>
+          <t>746929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>910677</t>
+          <t>769258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1526128</t>
+          <t>1489815</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503558</t>
+          <t>1469388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1566177</t>
+          <t>1507109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932754</t>
+          <t>811571</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932754</t>
+          <t>811571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932754</t>
+          <t>811571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635718</t>
+          <t>1612788</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635718</t>
+          <t>1612788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635718</t>
+          <t>1612788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>78986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105630</t>
+          <t>112314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>83437</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>70708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88146</t>
+          <t>97563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>163666</t>
+          <t>178287</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141959</t>
+          <t>157945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>201515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>833861</t>
+          <t>891797</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817330</t>
+          <t>874333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849950</t>
+          <t>907661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1016949</t>
+          <t>1033796</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003370</t>
+          <t>1019670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031501</t>
+          <t>1046525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1850809</t>
+          <t>1925593</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1829128</t>
+          <t>1902365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872516</t>
+          <t>1945935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>922960</t>
+          <t>986647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>922960</t>
+          <t>986647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>922960</t>
+          <t>986647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014475</t>
+          <t>2103880</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014475</t>
+          <t>2103880</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014475</t>
+          <t>2103880</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>235490</t>
+          <t>295171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339621</t>
+          <t>360639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210216</t>
+          <t>265737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294073</t>
+          <t>316192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>484867</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617312</t>
+          <t>656432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>7,93%</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3152131</t>
+          <t>3196711</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3112379</t>
+          <t>3164232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3216510</t>
+          <t>3229700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3392676</t>
+          <t>3439215</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3362422</t>
+          <t>3414837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3446279</t>
+          <t>3465292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6544807</t>
+          <t>6635926</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6491183</t>
+          <t>6599468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6623628</t>
+          <t>6680475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>92,07%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
